--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-imaging-study.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-imaging-study.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="169">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Entrée DICOM Examen Imagerie</t>
+    <t>DICOM Examen Imagerie</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -515,7 +515,13 @@
     <t>Nombre d'instances d'imagerie composant l'examen</t>
   </si>
   <si>
-    <t>fr-lm-imaging-study.seriesEndpoint</t>
+    <t>fr-lm-imaging-study.studyCustodian</t>
+  </si>
+  <si>
+    <t>Organisation responsable de l'examen</t>
+  </si>
+  <si>
+    <t>fr-lm-imaging-study.studyEndpoint</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-endpoint
@@ -834,7 +840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ28"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.8125" customWidth="true" bestFit="true"/>
@@ -3500,7 +3506,7 @@
         <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -3512,13 +3518,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="M27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3575,7 +3581,7 @@
         <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>73</v>
@@ -3586,10 +3592,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3597,10 +3603,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3612,13 +3618,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="M28" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3669,18 +3675,118 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AH28" t="s" s="2">
+      <c r="G29" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI28" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
+      <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>73</v>
       </c>
     </row>
